--- a/site/tournage.xlsx
+++ b/site/tournage.xlsx
@@ -792,7 +792,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -1807,17 +1807,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Passer d'une technologie a un problème a resoudre</t>
+          <t>Poser ou identifier le bon problème avant de chercher la solution</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Utilisateur, client, beneficiaire, usage et proposition de valeur.</t>
+          <t>Validation, hypotheses, experimentation, pivot et apprentissage.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1863,17 +1863,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Poser ou identifier le bon problème avant de chercher la solution</t>
+          <t>Passer d'une technologie a un problème a resoudre</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Validation, hypotheses, experimentation, pivot et apprentissage.</t>
+          <t>Utilisateur, client, beneficiaire, usage et proposition de valeur.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Gregoire Burgé</t>
+          <t>Joël Nguyen</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>AgroParisTech</t>
+          <t>Institut d’Optique</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Gregoire Burgé</t>
+          <t>Joël Nguyen</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>AgroParisTech</t>
+          <t>Institut d’Optique</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>

--- a/site/tournage.xlsx
+++ b/site/tournage.xlsx
@@ -1287,12 +1287,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -3289,12 +3289,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>

--- a/site/tournage.xlsx
+++ b/site/tournage.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -624,7 +624,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
@@ -951,12 +951,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>

--- a/site/tournage.xlsx
+++ b/site/tournage.xlsx
@@ -1584,7 +1584,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">

--- a/site/tournage.xlsx
+++ b/site/tournage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Par journée" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Par numéro" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Par journée" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Par numéro" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
